--- a/OptiAppsCreator/data/users_import.xlsx
+++ b/OptiAppsCreator/data/users_import.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="13">
   <si>
     <t xml:space="preserve">email</t>
   </si>
@@ -38,6 +38,27 @@
   </si>
   <si>
     <t xml:space="preserve">rafa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">diegogabrieloliva@gmail.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pass1234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">diego</t>
+  </si>
+  <si>
+    <t xml:space="preserve">jfrancesconi@gmail.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">javier</t>
+  </si>
+  <si>
+    <t xml:space="preserve">miguelbagajewicz@gmail.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">miguel</t>
   </si>
 </sst>
 </file>
@@ -112,9 +133,13 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -134,10 +159,10 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultColWidth="11.55078125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:C5"/>
+  <sheetFormatPr defaultColWidth="11.5703125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="5.55"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="26.58"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="31.68"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="23.61"/>
   </cols>
@@ -162,6 +187,39 @@
       </c>
       <c r="C2" s="0" t="s">
         <v>5</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B3" s="0" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3" s="0" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="0" t="s">
+        <v>9</v>
+      </c>
+      <c r="B4" s="0" t="s">
+        <v>7</v>
+      </c>
+      <c r="C4" s="0" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B5" s="0" t="s">
+        <v>7</v>
+      </c>
+      <c r="C5" s="0" t="s">
+        <v>12</v>
       </c>
     </row>
   </sheetData>
